--- a/Excel/悖论模拟干员名单用户版.xlsx
+++ b/Excel/悖论模拟干员名单用户版.xlsx
@@ -3624,7 +3624,7 @@
       </c>
       <c r="AA26" s="5" t="inlineStr">
         <is>
-          <t>***maa://42235</t>
+          <t>**maa://42235</t>
         </is>
       </c>
       <c r="AC26" s="4" t="inlineStr">

--- a/Excel/悖论模拟干员名单用户版.xlsx
+++ b/Excel/悖论模拟干员名单用户版.xlsx
@@ -1423,7 +1423,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>更新日期：2024.12.08 15:46:46</t>
+          <t>更新日期：2024.12.10 13:19:52</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>maa://35926, maa://36258, maa://43904</t>
+          <t>maa://35926, maa://36258, *maa://43904</t>
         </is>
       </c>
       <c r="M31" s="1" t="n"/>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>maa://35931, *maa://43901</t>
+          <t>maa://35931, maa://43901</t>
         </is>
       </c>
       <c r="I46" s="1" t="n"/>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>maa://44405</t>
+          <t>**maa://44405</t>
         </is>
       </c>
       <c r="I64" s="1" t="n"/>

--- a/Excel/悖论模拟干员名单用户版.xlsx
+++ b/Excel/悖论模拟干员名单用户版.xlsx
@@ -1423,7 +1423,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>更新日期：2025.02.22 13:17:25</t>
+          <t>更新日期：2025.02.26 13:18:30</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
@@ -1582,11 +1582,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="1" t="n"/>
       <c r="J9" s="1" t="inlineStr">
         <is>
@@ -2428,7 +2424,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>maa://38786</t>
+          <t>*maa://38786</t>
         </is>
       </c>
       <c r="Y15" s="1" t="n"/>
@@ -3290,7 +3286,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>maa://27127, *maa://22751</t>
+          <t>*maa://27127, *maa://22751</t>
         </is>
       </c>
       <c r="M22" s="1" t="n"/>
@@ -3518,7 +3514,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>*maa://24368, **maa://46650</t>
+          <t>*maa://24368, *maa://46650</t>
         </is>
       </c>
       <c r="E24" s="1" t="n"/>

--- a/Excel/悖论模拟干员名单用户版.xlsx
+++ b/Excel/悖论模拟干员名单用户版.xlsx
@@ -1423,7 +1423,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>更新日期：2025.03.02 13:19:18</t>
+          <t>更新日期：2025.03.03 13:19:02</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>*maa://24368, *maa://46650</t>
+          <t>*maa://24368, **maa://46650</t>
         </is>
       </c>
       <c r="E24" s="1" t="n"/>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>maa://28432, *maa://28440, maa://31400, *maa://28650</t>
+          <t>maa://28432, maa://28440, maa://31400, *maa://28650</t>
         </is>
       </c>
       <c r="M29" s="1" t="n"/>

--- a/Excel/悖论模拟干员名单用户版.xlsx
+++ b/Excel/悖论模拟干员名单用户版.xlsx
@@ -1423,7 +1423,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>更新日期：2025.03.02 13:19:18</t>
+          <t>更新日期：2025.03.05 13:18:50</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>***maa://34206, ***maa://39243, *maa://45271</t>
+          <t>***maa://39243, *maa://45271</t>
         </is>
       </c>
       <c r="E10" s="1" t="n"/>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>*maa://24368, *maa://46650</t>
+          <t>*maa://24368, **maa://46650</t>
         </is>
       </c>
       <c r="E24" s="1" t="n"/>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>maa://28432, *maa://28440, maa://31400, *maa://28650</t>
+          <t>maa://28432, maa://28440, maa://31400, *maa://28650</t>
         </is>
       </c>
       <c r="M29" s="1" t="n"/>

--- a/Excel/悖论模拟干员名单用户版.xlsx
+++ b/Excel/悖论模拟干员名单用户版.xlsx
@@ -1423,7 +1423,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>更新日期：2025.03.08 16:37:02</t>
+          <t>更新日期：2025.03.09 13:14:58</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>**maa://42324</t>
+          <t>*maa://42324</t>
         </is>
       </c>
       <c r="U17" s="1" t="n"/>

--- a/Excel/悖论模拟干员名单用户版.xlsx
+++ b/Excel/悖论模拟干员名单用户版.xlsx
@@ -1423,7 +1423,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>更新日期：2025.03.08 16:37:02</t>
+          <t>更新日期：2025.03.10 13:15:47</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>maa://21867, **maa://45826</t>
+          <t>maa://21867, ***maa://45826</t>
         </is>
       </c>
       <c r="I12" s="1" t="n"/>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>**maa://42324</t>
+          <t>*maa://42324</t>
         </is>
       </c>
       <c r="U17" s="1" t="n"/>

--- a/Excel/悖论模拟干员名单用户版.xlsx
+++ b/Excel/悖论模拟干员名单用户版.xlsx
@@ -1423,7 +1423,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>更新日期：2025.03.20 13:18:45</t>
+          <t>更新日期：2025.03.21 13:18:27</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">

--- a/Excel/悖论模拟干员名单用户版.xlsx
+++ b/Excel/悖论模拟干员名单用户版.xlsx
@@ -1423,7 +1423,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>更新日期：2025.03.28 13:20:26</t>
+          <t>更新日期：2025.03.29 13:18:03</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">

--- a/Excel/悖论模拟干员名单用户版.xlsx
+++ b/Excel/悖论模拟干员名单用户版.xlsx
@@ -1015,12 +1015,12 @@
       </c>
       <c r="AE4" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF4" s="2" t="inlineStr">
         <is>
-          <t>*maa://30062, *maa://39394, maa://48095</t>
+          <t>*maa://30062, *maa://39394</t>
         </is>
       </c>
       <c r="AG4" s="1" t="n"/>
@@ -1423,7 +1423,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>更新日期：2025.04.17 13:19:49</t>
+          <t>更新日期：2025.04.19 13:19:27</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>*maa://49976, maa://50085</t>
+          <t>maa://49976, maa://50085</t>
         </is>
       </c>
       <c r="Y20" s="1" t="n"/>

--- a/Excel/悖论模拟干员名单用户版.xlsx
+++ b/Excel/悖论模拟干员名单用户版.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>maa://39402, *maa://24633, *maa://30515, *maa://34787, ***maa://29083, **maa://54304</t>
+          <t>maa://39402, *maa://24633, *maa://30515, *maa://34787, ***maa://29083, *maa://54304</t>
         </is>
       </c>
       <c r="M2" s="1" t="n"/>
@@ -826,7 +826,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>maa://21249, maa://26254, **maa://22738</t>
+          <t>maa://21249, maa://26254, *maa://22738</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n"/>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>maa://52754</t>
+          <t>*maa://52754</t>
         </is>
       </c>
       <c r="Y6" s="1" t="n"/>
@@ -1423,7 +1423,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>更新日期：2025.05.24 13:19:10</t>
+          <t>更新日期：2025.05.31 13:19:45</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>**maa://47450</t>
+          <t>**maa://47450, maa://56348</t>
         </is>
       </c>
       <c r="I9" s="1" t="n"/>
@@ -2004,11 +2004,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="P12" s="2" t="inlineStr"/>
       <c r="Q12" s="1" t="n"/>
       <c r="R12" s="1" t="inlineStr">
         <is>
@@ -2651,12 +2647,12 @@
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>maa://23890, *maa://24940</t>
+          <t>maa://23890, *maa://24940, maa://56238</t>
         </is>
       </c>
       <c r="Q17" s="1" t="n"/>
@@ -2943,12 +2939,12 @@
       </c>
       <c r="W19" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>maa://31386</t>
+          <t>maa://31386, maa://58490</t>
         </is>
       </c>
       <c r="Y19" s="1" t="n"/>
@@ -3014,7 +3010,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>maa://22864, ***maa://43283, *maa://53361</t>
+          <t>maa://22864, ***maa://43283, **maa://53361</t>
         </is>
       </c>
       <c r="I20" s="1" t="n"/>
@@ -3773,12 +3769,12 @@
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>maa://41802</t>
+          <t>maa://41802, maa://56374</t>
         </is>
       </c>
       <c r="E26" s="1" t="n"/>
@@ -3821,12 +3817,12 @@
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>*maa://30968, maa://39870</t>
+          <t>*maa://30968, maa://39870, maa://56625</t>
         </is>
       </c>
       <c r="Q26" s="1" t="n"/>
@@ -3924,7 +3920,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>*maa://39601, **maa://21283, maa://34494, **maa://36665</t>
+          <t>*maa://39601, **maa://21283, maa://34494, *maa://36665</t>
         </is>
       </c>
       <c r="I27" s="1" t="n"/>
@@ -4519,14 +4515,10 @@
       </c>
       <c r="AA31" s="1" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>***maa://51420</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
       <c r="AC31" s="1" t="n"/>
       <c r="AD31" s="1" t="inlineStr">
         <is>
@@ -4861,12 +4853,12 @@
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>maa://48817</t>
+          <t>maa://48817, maa://56235</t>
         </is>
       </c>
       <c r="Q34" s="1" t="n"/>
@@ -6030,12 +6022,12 @@
       </c>
       <c r="G47" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>maa://27410, maa://29661, maa://28038</t>
+          <t>maa://27410, maa://29661, maa://28038, maa://56236</t>
         </is>
       </c>
       <c r="I47" s="1" t="n"/>

--- a/Excel/悖论模拟干员名单用户版.xlsx
+++ b/Excel/悖论模拟干员名单用户版.xlsx
@@ -755,12 +755,12 @@
       </c>
       <c r="AE2" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF2" s="2" t="inlineStr">
         <is>
-          <t>maa://25251, **maa://21730, **maa://36675</t>
+          <t>maa://25251, **maa://21730, **maa://36675, maa://59087</t>
         </is>
       </c>
       <c r="AG2" s="1" t="n"/>
@@ -826,7 +826,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>maa://21249, maa://26254, **maa://22738</t>
+          <t>maa://21249, maa://26254, *maa://22738</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n"/>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>maa://52754</t>
+          <t>*maa://52754</t>
         </is>
       </c>
       <c r="Y6" s="1" t="n"/>
@@ -1423,7 +1423,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>更新日期：2025.05.24 13:19:10</t>
+          <t>更新日期：2025.06.07 13:19:20</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>**maa://47450</t>
+          <t>**maa://47450, maa://56348</t>
         </is>
       </c>
       <c r="I9" s="1" t="n"/>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>***maa://34206, *maa://45271, ***maa://39243, maa://54000</t>
+          <t>***maa://34206, *maa://45271, ***maa://39243, **maa://54000</t>
         </is>
       </c>
       <c r="E10" s="1" t="n"/>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>maa://57541</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n"/>
@@ -2651,12 +2651,12 @@
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>maa://23890, *maa://24940</t>
+          <t>maa://23890, *maa://24940, maa://56238</t>
         </is>
       </c>
       <c r="Q17" s="1" t="n"/>
@@ -2943,12 +2943,12 @@
       </c>
       <c r="W19" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>maa://31386</t>
+          <t>maa://31386, maa://58490</t>
         </is>
       </c>
       <c r="Y19" s="1" t="n"/>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>maa://22864, ***maa://43283, *maa://53361</t>
+          <t>maa://22864, **maa://53361, ***maa://43283</t>
         </is>
       </c>
       <c r="I20" s="1" t="n"/>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>***maa://28036, **maa://41753</t>
+          <t>***maa://28036, *maa://41753</t>
         </is>
       </c>
       <c r="E23" s="1" t="n"/>
@@ -3773,12 +3773,12 @@
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>maa://41802</t>
+          <t>maa://41802, maa://56374</t>
         </is>
       </c>
       <c r="E26" s="1" t="n"/>
@@ -3789,12 +3789,12 @@
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>maa://24913</t>
+          <t>maa://24913, **maa://56240</t>
         </is>
       </c>
       <c r="I26" s="1" t="n"/>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>*maa://30968, maa://39870</t>
+          <t>*maa://30968, maa://39870, maa://56625</t>
         </is>
       </c>
       <c r="Q26" s="1" t="n"/>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>*maa://39601, **maa://21283, maa://34494, **maa://36665</t>
+          <t>*maa://39601, **maa://21283, maa://34494, *maa://36665</t>
         </is>
       </c>
       <c r="I27" s="1" t="n"/>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="AF29" s="2" t="inlineStr">
         <is>
-          <t>*maa://24080, maa://42865</t>
+          <t>*maa://24080, *maa://42865</t>
         </is>
       </c>
       <c r="AG29" s="1" t="n"/>
@@ -4519,14 +4519,10 @@
       </c>
       <c r="AA31" s="1" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>***maa://51420</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
       <c r="AC31" s="1" t="n"/>
       <c r="AD31" s="1" t="inlineStr">
         <is>
@@ -4861,12 +4857,12 @@
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>maa://48817</t>
+          <t>maa://48817, maa://56235</t>
         </is>
       </c>
       <c r="Q34" s="1" t="n"/>
@@ -4909,12 +4905,12 @@
       </c>
       <c r="AA34" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AC34" s="1" t="n"/>
@@ -4930,7 +4926,7 @@
       </c>
       <c r="AF34" s="2" t="inlineStr">
         <is>
-          <t>*maa://32650</t>
+          <t>maa://32650</t>
         </is>
       </c>
       <c r="AG34" s="1" t="n"/>
@@ -5224,7 +5220,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>maa://45718, maa://47069, maa://45789, maa://56336</t>
+          <t>maa://45718, maa://47069, maa://56336, maa://45789</t>
         </is>
       </c>
       <c r="M37" s="1" t="n"/>
@@ -5408,7 +5404,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>maa://36670, maa://25199, maa://30434, maa://45059, *maa://44165</t>
+          <t>maa://36670, maa://25199, maa://30434, *maa://45059, *maa://44165</t>
         </is>
       </c>
       <c r="I39" s="1" t="n"/>
@@ -5560,6 +5556,22 @@
         </is>
       </c>
       <c r="U40" s="1" t="n"/>
+      <c r="Z40" s="1" t="inlineStr">
+        <is>
+          <t>酒神</t>
+        </is>
+      </c>
+      <c r="AA40" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB40" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC40" s="1" t="n"/>
       <c r="AD40" s="1" t="inlineStr">
         <is>
           <t>云迹</t>
@@ -6018,6 +6030,22 @@
         </is>
       </c>
       <c r="U46" s="1" t="n"/>
+      <c r="AD46" s="1" t="inlineStr">
+        <is>
+          <t>蒂比</t>
+        </is>
+      </c>
+      <c r="AE46" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF46" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG46" s="1" t="n"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="B47" s="3" t="n"/>
@@ -6030,12 +6058,12 @@
       </c>
       <c r="G47" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>maa://27410, maa://29661, maa://28038</t>
+          <t>maa://27410, maa://29661, maa://28038, maa://56236</t>
         </is>
       </c>
       <c r="I47" s="1" t="n"/>
@@ -6305,12 +6333,12 @@
       </c>
       <c r="O52" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>maa://59378, maa://59394</t>
         </is>
       </c>
       <c r="Q52" s="1" t="n"/>
@@ -6364,6 +6392,22 @@
         </is>
       </c>
       <c r="Q53" s="1" t="n"/>
+      <c r="R53" s="1" t="inlineStr">
+        <is>
+          <t>Miss.Christine</t>
+        </is>
+      </c>
+      <c r="S53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U53" s="1" t="n"/>
     </row>
     <row r="54">
       <c r="F54" s="1" t="inlineStr">
@@ -6551,12 +6595,12 @@
       </c>
       <c r="G63" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>maa://59534</t>
         </is>
       </c>
       <c r="I63" s="1" t="n"/>
